--- a/AAII_Financials/Quarterly/ORLNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORLNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>ORLNY</t>
   </si>
@@ -656,69 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +756,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +794,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +832,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +924,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +962,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1015,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1051,11 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1059,8 +1089,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1107,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1109,8 +1143,11 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1181,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,8 +1219,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1214,8 +1257,11 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1295,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1333,11 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,8 +1371,11 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1354,8 +1409,11 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1561,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1529,8 +1599,11 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1637,11 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1675,11 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1634,48 +1713,54 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,323 +1790,351 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6031000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7543700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7358900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6086100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7078900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5068500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2671700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2818900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2594600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2867300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3378400</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E42" s="3">
         <v>58000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>41700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>38500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7876500</v>
+        <v>7548300</v>
       </c>
       <c r="E43" s="3">
+        <v>8455700</v>
+      </c>
+      <c r="F43" s="3">
         <v>7234800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7046900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7722900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8841700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7014300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8140900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8445500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10110800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9204600</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6623400</v>
+      </c>
+      <c r="E44" s="3">
         <v>5311900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5416900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5544400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4932400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4274800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5324700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8447800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7978400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7732100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5732200</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3858800</v>
+        <v>3497500</v>
       </c>
       <c r="E45" s="3">
+        <v>3279600</v>
+      </c>
+      <c r="F45" s="3">
         <v>2092900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>960500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>947400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>742900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1283300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>819700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>737200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>869900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2525000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24007000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24972000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22356700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19690700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20808400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19044600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16584300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20261900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19821400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21743100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21161900</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>852000</v>
+      </c>
+      <c r="E47" s="3">
         <v>836300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>847900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>793800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>779600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>732600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>667100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>747300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>791700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>749600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>786000</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43156000</v>
+      </c>
+      <c r="E48" s="3">
         <v>42562200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>43745500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44307400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>43939400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40394400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37633200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>40271500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38741700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37974500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37816900</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2100400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2184200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2320200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2401000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3594100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2800500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2754400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2932400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3679100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4124300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3517700</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2206,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3434800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3443600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3733300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3586100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3565300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3592800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3381300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>907200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>881000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>760400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3439700</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2282,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74586100</v>
+      </c>
+      <c r="E54" s="3">
         <v>75036000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73755600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71553800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73459000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>67309900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>61794100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>65833000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64577700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66066400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>67267700</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2354,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5876400</v>
+      </c>
+      <c r="E57" s="3">
         <v>5270300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4278200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9760800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12200400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9818800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3960300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11216900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11211000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9914100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4080100</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1026400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1176100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>893300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>852100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>923000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>834000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1121900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>598700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>993900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>692600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1496100</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8188500</v>
+      </c>
+      <c r="E59" s="3">
         <v>8450600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8396300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3910300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4887000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4644400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6660100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4687100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6026400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9026800</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17757200</v>
+      </c>
+      <c r="E60" s="3">
         <v>18271400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16744200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14600200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18089400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15370800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14595000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15884000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16960200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16704200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17675700</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9801500</v>
+      </c>
+      <c r="E61" s="3">
         <v>9306000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9694500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9099200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8169700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7019800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6015500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5313900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4964700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5170600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5091700</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3392500</v>
+      </c>
+      <c r="E62" s="3">
         <v>3700700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3531600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3331500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3315300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3054800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2903900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2889400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2786400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2789600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2415600</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2694,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34994000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35061500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33533200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30575800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33104700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28417600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26287200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27202700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27527700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27449300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28244400</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2900,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>26338300</v>
+      </c>
+      <c r="E72" s="3">
         <v>27021300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25846200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26934700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26528000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>26134900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23528400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25657000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24394600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>25838500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>25559500</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3052,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39334000</v>
+      </c>
+      <c r="E76" s="3">
         <v>39716400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39964700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>40678100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>40059200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38627500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35270000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>38355400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>36778100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38337300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>38744000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3128,54 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3014,8 +3209,11 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3227,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>966500</v>
+      </c>
+      <c r="E83" s="3">
         <v>864000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>811800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>875900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>871000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>843000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>781600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>778600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>830400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>887500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>732400</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4042800</v>
+      </c>
+      <c r="E89" s="3">
         <v>2272800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3553800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2259700</v>
       </c>
-      <c r="G89" s="3">
-        <v>2903900</v>
-      </c>
       <c r="H89" s="3">
+        <v>2884000</v>
+      </c>
+      <c r="I89" s="3">
         <v>4046300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2523300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2231400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1483100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2931600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1304800</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3509,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1848400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1843400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1743700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2004000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1752200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-1731700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1738800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1684000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1741200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1659000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2077700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2401100</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3244700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1808500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2811400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2023500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1791000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1771000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1734400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2616000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1725600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2456300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1940000</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,43 +3677,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>2468400</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>1915700</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>1165500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>300</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +3827,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2232700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-60700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>456400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1231300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>523300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-60100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>133800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-441000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-916600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>750300</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-33600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>10400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-27900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-128400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>83600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-217700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-43400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1438600</v>
+      </c>
+      <c r="E102" s="3">
         <v>445800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1199600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-944500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1642900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2218200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>51500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>103300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-244200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-469300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13200</v>
       </c>
     </row>
